--- a/content/MtA Вальс Сломанных Кукол/мискеллания/Рене и мегаопыт.xlsx
+++ b/content/MtA Вальс Сломанных Кукол/мискеллания/Рене и мегаопыт.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Obsidian Circe\Rolling Vault\MtA Вальс Сломанных Кукол\-мискеллания\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Obsidian Circe\Rolling Vault\MtA Вальс Сломанных Кукол\мискеллания\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0927812D-B20C-4E7B-AC4C-65A152573751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BB88BB-9B59-4381-B74A-040C743C561D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13759" xr2:uid="{8C796DC0-0E5B-43FF-B2DD-E20750249270}"/>
   </bookViews>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="107">
   <si>
     <t>Атрибут</t>
   </si>
@@ -413,6 +413,9 @@
   </si>
   <si>
     <t>4FB за точку (м.3)</t>
+  </si>
+  <si>
+    <t>главы</t>
   </si>
 </sst>
 </file>
@@ -2710,6 +2713,9 @@
       <c r="AA26" t="s">
         <v>93</v>
       </c>
+      <c r="AC26" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="27" spans="2:29" x14ac:dyDescent="0.3">
       <c r="B27" s="18" t="s">

--- a/content/MtA Вальс Сломанных Кукол/мискеллания/Рене и мегаопыт.xlsx
+++ b/content/MtA Вальс Сломанных Кукол/мискеллания/Рене и мегаопыт.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Obsidian Circe\Rolling Vault\MtA Вальс Сломанных Кукол\мискеллания\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90BB88BB-9B59-4381-B74A-040C743C561D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF591C8E-0268-4115-91CB-B1B21A8E02A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-118" yWindow="-118" windowWidth="25370" windowHeight="13759" xr2:uid="{8C796DC0-0E5B-43FF-B2DD-E20750249270}"/>
   </bookViews>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="110">
   <si>
     <t>Атрибут</t>
   </si>
@@ -416,6 +416,15 @@
   </si>
   <si>
     <t>главы</t>
+  </si>
+  <si>
+    <t>опыт</t>
+  </si>
+  <si>
+    <t>после конклава</t>
+  </si>
+  <si>
+    <t>Эмпатия</t>
   </si>
 </sst>
 </file>
@@ -571,7 +580,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -602,6 +611,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -625,7 +640,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
@@ -678,6 +693,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
@@ -685,7 +701,7 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{8FDA4460-39BB-40B1-9483-50C7FBA2CEAC}"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF9C5700"/>
@@ -693,6 +709,26 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1033,7 +1069,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58ED4DBB-4B9B-4D76-BD41-0582AD509625}">
-  <dimension ref="B1:AC41"/>
+  <dimension ref="B1:AD41"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="17.05" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.44140625" style="14" bestFit="1" customWidth="1"/>
@@ -1055,10 +1091,10 @@
     <col min="26" max="26" width="17" customWidth="1"/>
     <col min="27" max="27" width="9.21875" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="18.77734375" customWidth="1"/>
-    <col min="29" max="29" width="13.21875" customWidth="1"/>
+    <col min="29" max="29" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B1" s="12" t="s">
         <v>21</v>
       </c>
@@ -1134,12 +1170,12 @@
       <c r="Z1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" s="31" t="s">
+      <c r="AA1" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AB1" s="31"/>
-    </row>
-    <row r="2" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AB1" s="32"/>
+    </row>
+    <row r="2" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B2" s="15" t="s">
         <v>22</v>
       </c>
@@ -1170,12 +1206,12 @@
       <c r="Z2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="AA2" s="30" t="s">
+      <c r="AA2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="AB2" s="30"/>
-    </row>
-    <row r="3" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AB2" s="31"/>
+    </row>
+    <row r="3" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B3" s="18" t="s">
         <v>23</v>
       </c>
@@ -1236,12 +1272,12 @@
       <c r="Z3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="AA3" s="30" t="s">
+      <c r="AA3" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="AB3" s="30"/>
-    </row>
-    <row r="4" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AB3" s="31"/>
+    </row>
+    <row r="4" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B4" s="18" t="s">
         <v>24</v>
       </c>
@@ -1302,12 +1338,12 @@
       <c r="Z4" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="AA4" s="30" t="s">
+      <c r="AA4" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="AB4" s="30"/>
-    </row>
-    <row r="5" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AB4" s="31"/>
+    </row>
+    <row r="5" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B5" s="18" t="s">
         <v>25</v>
       </c>
@@ -1317,7 +1353,7 @@
       </c>
       <c r="D5" s="18" t="str">
         <f>C5&amp;REPT("•",COUNTIF($G5:$L5,"@"))</f>
-        <v>••</v>
+        <v>•••</v>
       </c>
       <c r="E5" s="18">
         <f t="shared" si="5"/>
@@ -1325,7 +1361,7 @@
       </c>
       <c r="F5" s="18">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>89</v>
@@ -1333,7 +1369,9 @@
       <c r="H5" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="I5" s="20"/>
+      <c r="I5" s="20" t="s">
+        <v>88</v>
+      </c>
       <c r="J5" s="20"/>
       <c r="K5" s="20"/>
       <c r="M5" s="18" t="s">
@@ -1372,12 +1410,12 @@
       <c r="Z5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AA5" s="30" t="s">
+      <c r="AA5" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="AB5" s="30"/>
-    </row>
-    <row r="6" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AB5" s="31"/>
+    </row>
+    <row r="6" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B6" s="15" t="s">
         <v>26</v>
       </c>
@@ -1420,10 +1458,10 @@
       <c r="Z6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="AA6" s="30"/>
-      <c r="AB6" s="30"/>
-    </row>
-    <row r="7" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AA6" s="31"/>
+      <c r="AB6" s="31"/>
+    </row>
+    <row r="7" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B7" s="18" t="s">
         <v>27</v>
       </c>
@@ -1488,12 +1526,12 @@
       <c r="Z7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="AA7" s="30" t="s">
+      <c r="AA7" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="AB7" s="30"/>
-    </row>
-    <row r="8" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AB7" s="31"/>
+    </row>
+    <row r="8" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B8" s="18" t="s">
         <v>28</v>
       </c>
@@ -1556,12 +1594,12 @@
       <c r="Z8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA8" s="30" t="s">
+      <c r="AA8" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="AB8" s="30"/>
-    </row>
-    <row r="9" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AB8" s="31"/>
+    </row>
+    <row r="9" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B9" s="21" t="s">
         <v>29</v>
       </c>
@@ -1619,7 +1657,7 @@
       <c r="U9" s="20"/>
       <c r="V9" s="20"/>
     </row>
-    <row r="10" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B10" s="15" t="s">
         <v>30</v>
       </c>
@@ -1671,11 +1709,14 @@
       <c r="AB10" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="AC10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AC10" s="30" t="s">
+        <v>108</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B11" s="21" t="s">
         <v>31</v>
       </c>
@@ -1747,10 +1788,14 @@
       </c>
       <c r="AC11" s="10">
         <f>SUM(F3:F13)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:29" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+      <c r="AD11" s="10">
+        <f>SUM(F3:F13)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B12" s="18" t="s">
         <v>32</v>
       </c>
@@ -1826,8 +1871,12 @@
         <f>SUM(F15:F23)</f>
         <v>26</v>
       </c>
-    </row>
-    <row r="13" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD12" s="10">
+        <f>SUM(F15:F23)</f>
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B13" s="18" t="s">
         <v>33</v>
       </c>
@@ -1887,8 +1936,12 @@
         <f>SUM(F25)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD13" s="10">
+        <f>SUM(F25)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B14" s="12" t="s">
         <v>34</v>
       </c>
@@ -1944,8 +1997,12 @@
         <f>SUM(F26)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD14" s="10">
+        <f>SUM(F26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B15" s="21" t="s">
         <v>35</v>
       </c>
@@ -1954,7 +2011,7 @@
         <v>••</v>
       </c>
       <c r="D15" s="18" t="str">
-        <f t="shared" ref="D15:D23" si="15">C15&amp;REPT("•",COUNTIF($G15:$L15,"@"))</f>
+        <f>C15&amp;REPT("•",COUNTIF($G15:$L15,"@"))</f>
         <v>•••</v>
       </c>
       <c r="E15" s="18">
@@ -1962,7 +2019,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="18">
-        <f t="shared" ref="F15:F23" si="16">IF(D15=C15,0,E15)</f>
+        <f t="shared" ref="F15:F23" si="15">IF(D15=C15,0,E15)</f>
         <v>16</v>
       </c>
       <c r="G15" s="20" t="s">
@@ -2019,8 +2076,12 @@
         <f>SUM(F27)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="2:29" ht="17.7" x14ac:dyDescent="0.35">
+      <c r="AD15" s="10">
+        <f>SUM(F27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:30" ht="17.7" x14ac:dyDescent="0.35">
       <c r="B16" s="23" t="s">
         <v>36</v>
       </c>
@@ -2029,7 +2090,7 @@
         <v>••</v>
       </c>
       <c r="D16" s="18" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" ref="D16:D23" si="16">C16&amp;REPT("•",COUNTIF($G16:$L16,"@"))</f>
         <v>••</v>
       </c>
       <c r="E16" s="18">
@@ -2037,7 +2098,7 @@
         <v>14</v>
       </c>
       <c r="F16" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G16" s="20" t="s">
@@ -2094,8 +2155,12 @@
         <f>SUM(F30:F37)</f>
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="2:29" x14ac:dyDescent="0.3">
+      <c r="AD16" s="10">
+        <f>SUM(F30:F37)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B17" s="18" t="s">
         <v>37</v>
       </c>
@@ -2104,7 +2169,7 @@
         <v/>
       </c>
       <c r="D17" s="18" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="E17" s="18">
@@ -2112,7 +2177,7 @@
         <v>10</v>
       </c>
       <c r="F17" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G17" s="20"/>
@@ -2159,10 +2224,14 @@
       </c>
       <c r="AC17" s="11">
         <f>SUM(Q3:Q45)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:29" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+      <c r="AD17" s="11">
+        <f>SUM(Q3:Q45)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B18" s="18" t="s">
         <v>38</v>
       </c>
@@ -2171,7 +2240,7 @@
         <v/>
       </c>
       <c r="D18" s="18" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="E18" s="18">
@@ -2179,7 +2248,7 @@
         <v>10</v>
       </c>
       <c r="F18" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G18" s="20"/>
@@ -2221,7 +2290,7 @@
       <c r="AA18" s="10"/>
       <c r="AB18" s="10"/>
     </row>
-    <row r="19" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B19" s="18" t="s">
         <v>39</v>
       </c>
@@ -2230,7 +2299,7 @@
         <v/>
       </c>
       <c r="D19" s="18" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="E19" s="18">
@@ -2238,7 +2307,7 @@
         <v>10</v>
       </c>
       <c r="F19" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G19" s="20"/>
@@ -2286,11 +2355,15 @@
         <v>57</v>
       </c>
       <c r="AC19">
-        <f>19+22</f>
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="2:29" x14ac:dyDescent="0.3">
+        <f>19+29+3</f>
+        <v>51</v>
+      </c>
+      <c r="AD19">
+        <f>19+29+3</f>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B20" s="18" t="s">
         <v>40</v>
       </c>
@@ -2299,7 +2372,7 @@
         <v/>
       </c>
       <c r="D20" s="18" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>•</v>
       </c>
       <c r="E20" s="18">
@@ -2307,7 +2380,7 @@
         <v>10</v>
       </c>
       <c r="F20" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>10</v>
       </c>
       <c r="G20" s="20" t="s">
@@ -2359,10 +2432,14 @@
       </c>
       <c r="AC20" s="10">
         <f t="shared" si="18"/>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" spans="2:29" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="AD20" s="10">
+        <f t="shared" ref="AD20" si="19">SUM(AD11:AD17)</f>
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B21" s="18" t="s">
         <v>41</v>
       </c>
@@ -2371,7 +2448,7 @@
         <v/>
       </c>
       <c r="D21" s="18" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="E21" s="18">
@@ -2379,7 +2456,7 @@
         <v>10</v>
       </c>
       <c r="F21" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G21" s="20"/>
@@ -2418,10 +2495,14 @@
       <c r="AB21" s="10"/>
       <c r="AC21" s="10">
         <f>AC19-AC20</f>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="22" spans="2:29" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="AD21" s="10">
+        <f>AD19-AD20</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B22" s="18" t="s">
         <v>42</v>
       </c>
@@ -2430,7 +2511,7 @@
         <v/>
       </c>
       <c r="D22" s="18" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v/>
       </c>
       <c r="E22" s="18">
@@ -2438,7 +2519,7 @@
         <v>10</v>
       </c>
       <c r="F22" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G22" s="20"/>
@@ -2480,7 +2561,7 @@
       <c r="AA22" s="10"/>
       <c r="AB22" s="10"/>
     </row>
-    <row r="23" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B23" s="21" t="s">
         <v>43</v>
       </c>
@@ -2489,7 +2570,7 @@
         <v>•••</v>
       </c>
       <c r="D23" s="18" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>•••</v>
       </c>
       <c r="E23" s="18">
@@ -2497,7 +2578,7 @@
         <v>24</v>
       </c>
       <c r="F23" s="18">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>0</v>
       </c>
       <c r="G23" s="20" t="s">
@@ -2545,7 +2626,7 @@
       <c r="AA23" s="10"/>
       <c r="AB23" s="10"/>
     </row>
-    <row r="24" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B24" s="12" t="s">
         <v>44</v>
       </c>
@@ -2580,7 +2661,7 @@
       <c r="AA24" s="10"/>
       <c r="AB24" s="10"/>
     </row>
-    <row r="25" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B25" s="18" t="s">
         <v>6</v>
       </c>
@@ -2615,11 +2696,11 @@
         <v>76</v>
       </c>
       <c r="N25" s="19" t="str">
-        <f t="shared" ref="N25:N34" si="19">REPT("•",COUNTIF($R25:$X25,"•"))</f>
+        <f t="shared" ref="N25:N34" si="20">REPT("•",COUNTIF($R25:$X25,"•"))</f>
         <v>•</v>
       </c>
       <c r="O25" s="18" t="str">
-        <f t="shared" ref="O25:O34" si="20">N25&amp;REPT("•",COUNTIF($R25:$X25,"@"))</f>
+        <f t="shared" ref="O25:O34" si="21">N25&amp;REPT("•",COUNTIF($R25:$X25,"@"))</f>
         <v>•</v>
       </c>
       <c r="P25" s="18">
@@ -2627,7 +2708,7 @@
         <v>2</v>
       </c>
       <c r="Q25" s="18">
-        <f t="shared" ref="Q25:Q34" si="21">IF(N25=O25,0,VLOOKUP("_"&amp;LEN(N25)&amp;LEN(O25),skillblock,4,0))</f>
+        <f t="shared" ref="Q25:Q36" si="22">IF(N25=O25,0,VLOOKUP("_"&amp;LEN(N25)&amp;LEN(O25),skillblock,4,0))</f>
         <v>0</v>
       </c>
       <c r="R25" s="20" t="s">
@@ -2638,7 +2719,7 @@
       <c r="U25" s="20"/>
       <c r="V25" s="20"/>
     </row>
-    <row r="26" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B26" s="18" t="s">
         <v>45</v>
       </c>
@@ -2655,7 +2736,7 @@
         <v>6</v>
       </c>
       <c r="F26" s="18">
-        <f t="shared" ref="F26:F27" si="22">IF(D26=C26,0,E26)</f>
+        <f t="shared" ref="F26:F27" si="23">IF(D26=C26,0,E26)</f>
         <v>0</v>
       </c>
       <c r="G26" s="20" t="s">
@@ -2680,11 +2761,11 @@
         <v>77</v>
       </c>
       <c r="N26" s="19" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>••</v>
       </c>
       <c r="O26" s="18" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>••</v>
       </c>
       <c r="P26" s="18">
@@ -2692,7 +2773,7 @@
         <v>4</v>
       </c>
       <c r="Q26" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R26" s="20" t="s">
@@ -2717,7 +2798,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B27" s="18" t="s">
         <v>11</v>
       </c>
@@ -2733,7 +2814,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="18">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="G27" s="20" t="s">
@@ -2749,11 +2830,11 @@
         <v>78</v>
       </c>
       <c r="N27" s="19" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>•</v>
       </c>
       <c r="O27" s="18" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>•</v>
       </c>
       <c r="P27" s="18">
@@ -2761,7 +2842,7 @@
         <v>2</v>
       </c>
       <c r="Q27" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R27" s="20" t="s">
@@ -2785,7 +2866,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B28" s="18"/>
       <c r="C28" s="19"/>
       <c r="D28" s="18"/>
@@ -2800,11 +2881,11 @@
         <v>79</v>
       </c>
       <c r="N28" s="19" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>•••</v>
       </c>
       <c r="O28" s="18" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>•••</v>
       </c>
       <c r="P28" s="18">
@@ -2812,7 +2893,7 @@
         <v>6</v>
       </c>
       <c r="Q28" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R28" s="20" t="s">
@@ -2827,7 +2908,7 @@
       <c r="U28" s="20"/>
       <c r="V28" s="20"/>
       <c r="X28" t="str">
-        <f t="shared" ref="X28:X41" si="23">"_"&amp;Y28&amp;Z28</f>
+        <f t="shared" ref="X28:X41" si="24">"_"&amp;Y28&amp;Z28</f>
         <v>_02</v>
       </c>
       <c r="Y28">
@@ -2841,7 +2922,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B29" s="12" t="s">
         <v>46</v>
       </c>
@@ -2858,11 +2939,11 @@
         <v>80</v>
       </c>
       <c r="N29" s="19" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>••</v>
       </c>
       <c r="O29" s="18" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>••</v>
       </c>
       <c r="P29" s="18">
@@ -2870,7 +2951,7 @@
         <v>4</v>
       </c>
       <c r="Q29" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R29" s="27" t="s">
@@ -2883,7 +2964,7 @@
       <c r="U29" s="20"/>
       <c r="V29" s="20"/>
       <c r="X29" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>_03</v>
       </c>
       <c r="Y29">
@@ -2897,7 +2978,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B30" s="18" t="s">
         <v>47</v>
       </c>
@@ -2930,11 +3011,11 @@
         <v>81</v>
       </c>
       <c r="N30" s="19" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>••</v>
       </c>
       <c r="O30" s="18" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>••</v>
       </c>
       <c r="P30" s="18">
@@ -2942,7 +3023,7 @@
         <v>4</v>
       </c>
       <c r="Q30" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R30" s="20" t="s">
@@ -2955,7 +3036,7 @@
       <c r="U30" s="20"/>
       <c r="V30" s="20"/>
       <c r="X30" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>_04</v>
       </c>
       <c r="Y30">
@@ -2969,7 +3050,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B31" s="18" t="s">
         <v>48</v>
       </c>
@@ -2982,11 +3063,11 @@
         <v>•••</v>
       </c>
       <c r="E31" s="18">
-        <f t="shared" ref="E31:E34" si="24">LEN(C31)*3</f>
+        <f t="shared" ref="E31:E34" si="25">LEN(C31)*3</f>
         <v>6</v>
       </c>
       <c r="F31" s="18">
-        <f t="shared" ref="F31:F36" si="25">IF(D31=C31,0,E31)</f>
+        <f t="shared" ref="F31:F36" si="26">IF(D31=C31,0,E31)</f>
         <v>6</v>
       </c>
       <c r="G31" s="20" t="s">
@@ -3004,20 +3085,20 @@
         <v>82</v>
       </c>
       <c r="N31" s="19" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>••</v>
       </c>
       <c r="O31" s="18" t="str">
-        <f t="shared" si="20"/>
-        <v>••</v>
+        <f t="shared" si="21"/>
+        <v>•••</v>
       </c>
       <c r="P31" s="18">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
       <c r="Q31" s="18">
-        <f t="shared" si="21"/>
-        <v>0</v>
+        <f t="shared" si="22"/>
+        <v>4</v>
       </c>
       <c r="R31" s="20" t="s">
         <v>89</v>
@@ -3025,11 +3106,13 @@
       <c r="S31" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="T31" s="20"/>
+      <c r="T31" s="20" t="s">
+        <v>88</v>
+      </c>
       <c r="U31" s="20"/>
       <c r="V31" s="20"/>
       <c r="X31" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>_05</v>
       </c>
       <c r="Y31">
@@ -3043,7 +3126,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="2:29" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:30" x14ac:dyDescent="0.3">
       <c r="B32" s="18" t="s">
         <v>49</v>
       </c>
@@ -3056,11 +3139,11 @@
         <v>••</v>
       </c>
       <c r="E32" s="18">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>6</v>
       </c>
       <c r="F32" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G32" s="20" t="s">
@@ -3076,11 +3159,11 @@
         <v>83</v>
       </c>
       <c r="N32" s="19" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="O32" s="18" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="P32" s="18">
@@ -3088,7 +3171,7 @@
         <v>3</v>
       </c>
       <c r="Q32" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R32" s="20"/>
@@ -3097,7 +3180,7 @@
       <c r="U32" s="20"/>
       <c r="V32" s="20"/>
       <c r="X32" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>_12</v>
       </c>
       <c r="Y32">
@@ -3124,11 +3207,11 @@
         <v>•</v>
       </c>
       <c r="E33" s="18">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>3</v>
       </c>
       <c r="F33" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G33" s="20" t="s">
@@ -3142,11 +3225,11 @@
         <v>84</v>
       </c>
       <c r="N33" s="19" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>••</v>
       </c>
       <c r="O33" s="18" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>••</v>
       </c>
       <c r="P33" s="18">
@@ -3154,7 +3237,7 @@
         <v>4</v>
       </c>
       <c r="Q33" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R33" s="20" t="s">
@@ -3167,7 +3250,7 @@
       <c r="U33" s="20"/>
       <c r="V33" s="20"/>
       <c r="X33" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>_13</v>
       </c>
       <c r="Y33">
@@ -3177,7 +3260,7 @@
         <v>3</v>
       </c>
       <c r="AA33" s="7">
-        <f t="shared" ref="AA33:AA41" si="26">(Z33-Y33)*(Z33+Y33-1)</f>
+        <f t="shared" ref="AA33:AA41" si="27">(Z33-Y33)*(Z33+Y33-1)</f>
         <v>6</v>
       </c>
     </row>
@@ -3194,11 +3277,11 @@
         <v>•</v>
       </c>
       <c r="E34" s="18">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>3</v>
       </c>
       <c r="F34" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G34" s="20" t="s">
@@ -3212,11 +3295,11 @@
         <v>85</v>
       </c>
       <c r="N34" s="19" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v>••</v>
       </c>
       <c r="O34" s="18" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v>••</v>
       </c>
       <c r="P34" s="18">
@@ -3224,7 +3307,7 @@
         <v>4</v>
       </c>
       <c r="Q34" s="18">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R34" s="20" t="s">
@@ -3237,7 +3320,7 @@
       <c r="U34" s="20"/>
       <c r="V34" s="20"/>
       <c r="X34" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>_14</v>
       </c>
       <c r="Y34">
@@ -3247,7 +3330,7 @@
         <v>4</v>
       </c>
       <c r="AA34" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>12</v>
       </c>
     </row>
@@ -3257,7 +3340,7 @@
       <c r="D35" s="18"/>
       <c r="E35" s="18"/>
       <c r="F35" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G35" s="20"/>
@@ -3278,7 +3361,7 @@
       <c r="U35" s="17"/>
       <c r="V35" s="17"/>
       <c r="X35" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>_15</v>
       </c>
       <c r="Y35">
@@ -3288,7 +3371,7 @@
         <v>5</v>
       </c>
       <c r="AA35" s="7">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>20</v>
       </c>
     </row>
@@ -3305,11 +3388,11 @@
         <v>•</v>
       </c>
       <c r="E36" s="18">
-        <f t="shared" ref="E36" si="27">LEN(C36)*3</f>
+        <f t="shared" ref="E36" si="28">LEN(C36)*3</f>
         <v>3</v>
       </c>
       <c r="F36" s="18">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="G36" s="27" t="s">
@@ -3327,15 +3410,15 @@
         <v>••</v>
       </c>
       <c r="O36" s="18" t="str">
-        <f>N36&amp;REPT("•",COUNTIF($R36:$X36,"@"))</f>
+        <f>N36&amp;REPT("•",COUNTIF($R36:$W36,"@"))</f>
         <v>••</v>
       </c>
       <c r="P36" s="18">
-        <f t="shared" ref="P36" si="28">IF(LEN(N36)=0,3,2*LEN(N36))</f>
+        <f>IF(LEN(N36)=0,3,2*LEN(N36))</f>
         <v>4</v>
       </c>
       <c r="Q36" s="18">
-        <f>IF(N36=O36,0,VLOOKUP("_"&amp;LEN(N36)&amp;LEN(O36),skillblock,4,0))</f>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="R36" s="27" t="s">
@@ -3348,7 +3431,7 @@
       <c r="U36" s="20"/>
       <c r="V36" s="20"/>
       <c r="X36" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>_23</v>
       </c>
       <c r="Y36">
@@ -3358,23 +3441,41 @@
         <v>3</v>
       </c>
       <c r="AA36" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>4</v>
       </c>
     </row>
     <row r="37" spans="2:27" x14ac:dyDescent="0.3">
-      <c r="M37" s="18"/>
-      <c r="N37" s="19"/>
-      <c r="O37" s="18"/>
-      <c r="P37" s="18"/>
-      <c r="Q37" s="18"/>
-      <c r="R37" s="20"/>
-      <c r="S37" s="20"/>
+      <c r="M37" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="N37" s="19" t="str">
+        <f>REPT("•",COUNTIF($R37:$X37,"•"))</f>
+        <v>•</v>
+      </c>
+      <c r="O37" s="18" t="str">
+        <f>N37&amp;REPT("•",COUNTIF($R37:$W37,"@"))</f>
+        <v>••</v>
+      </c>
+      <c r="P37" s="18">
+        <f t="shared" ref="P37" si="29">IF(LEN(N37)=0,3,2*LEN(N37))</f>
+        <v>2</v>
+      </c>
+      <c r="Q37" s="18">
+        <f>IF(N37=O37,0,VLOOKUP("_"&amp;LEN(N37)&amp;LEN(O37),skillblock,4,0))</f>
+        <v>2</v>
+      </c>
+      <c r="R37" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="S37" s="20" t="s">
+        <v>88</v>
+      </c>
       <c r="T37" s="20"/>
       <c r="U37" s="20"/>
       <c r="V37" s="20"/>
       <c r="X37" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>_24</v>
       </c>
       <c r="Y37">
@@ -3384,13 +3485,13 @@
         <v>4</v>
       </c>
       <c r="AA37" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10</v>
       </c>
     </row>
     <row r="38" spans="2:27" x14ac:dyDescent="0.3">
       <c r="X38" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>_25</v>
       </c>
       <c r="Y38">
@@ -3400,13 +3501,13 @@
         <v>5</v>
       </c>
       <c r="AA38" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>18</v>
       </c>
     </row>
     <row r="39" spans="2:27" x14ac:dyDescent="0.3">
       <c r="X39" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>_34</v>
       </c>
       <c r="Y39">
@@ -3416,13 +3517,13 @@
         <v>4</v>
       </c>
       <c r="AA39" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>6</v>
       </c>
     </row>
     <row r="40" spans="2:27" x14ac:dyDescent="0.3">
       <c r="X40" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>_35</v>
       </c>
       <c r="Y40">
@@ -3432,13 +3533,13 @@
         <v>5</v>
       </c>
       <c r="AA40" s="9">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>14</v>
       </c>
     </row>
     <row r="41" spans="2:27" x14ac:dyDescent="0.3">
       <c r="X41" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>_45</v>
       </c>
       <c r="Y41">
@@ -3448,7 +3549,7 @@
         <v>5</v>
       </c>
       <c r="AA41" s="6">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>8</v>
       </c>
     </row>
@@ -3469,22 +3570,32 @@
     <mergeCell ref="AA6:AB6"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F36">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G3:L36 R3:W36">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+  <conditionalFormatting sqref="G3:L36">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
       <formula>"@"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q3:Q36">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+  <conditionalFormatting sqref="Q3:Q37">
+    <cfRule type="cellIs" dxfId="3" priority="8" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z11:AC17">
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="notEqual">
+  <conditionalFormatting sqref="R37:S37">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"@"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R3:W36">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"@"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z11:AD17">
+    <cfRule type="cellIs" dxfId="0" priority="11" operator="notEqual">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
